--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16821.93</v>
+        <v>16721.11</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10694.74</v>
+        <v>10630.64</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1632.06</v>
+        <v>1622.28</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8578.07</v>
+        <v>8461.450000000001</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10549.64</v>
+        <v>10406.21</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22658.99</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17499.26</v>
+        <v>17593.49</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>22536.93</v>
+        <v>22788.97</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6439.12</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7798.24</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7174.39</v>
+        <v>7201.57</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5637.02</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1782.46</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>66743.77</v>
+        <v>66575.25999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13179.03</v>
+        <v>13145.76</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>61271.78</v>
+        <v>61853.9</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>55673.9</v>
+        <v>56088.66</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12526.21</v>
+        <v>12619.53</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6628.51</v>
+        <v>6677.89</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1806.8</v>
+        <v>1788.78</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>623.86</v>
+        <v>621.12</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2508.81</v>
+        <v>2497.81</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8873.209999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>22681.75</v>
+        <v>22582.33</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23862.63</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>40831.61</v>
+        <v>40387.43</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4344.74</v>
+        <v>4297.47</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>38501.05</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>38501.05</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10382.81</v>
+        <v>10269.86</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8321.84</v>
+        <v>8302.950000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>75.42</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>43072.51</v>
+        <v>42966.15</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10026.31</v>
+        <v>10001.56</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1737.89</v>
+        <v>1733.6</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>23171.93</v>
+        <v>23285.75</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>52860.96</v>
+        <v>53120.63</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15219.05</v>
+        <v>15269.54</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1667.6</v>
+        <v>1673.13</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2932.6</v>
+        <v>2941.94</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26736.84</v>
+        <v>26821.94</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>10750.44</v>
+        <v>10807.6</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>401052.58</v>
+        <v>403185.16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -623,7 +623,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1550,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2164,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2534,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/may-2026.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
